--- a/tests/data/expected_log40.xlsx
+++ b/tests/data/expected_log40.xlsx
@@ -150,6 +150,7 @@
           </a:p>
         </rich>
       </tx>
+      <overlay val="0"/>
     </title>
     <plotArea>
       <scatterChart>
@@ -178,7 +179,7 @@
           </marker>
           <xVal>
             <numRef>
-              <f>'解析'!$A$7:$A$14</f>
+              <f>'解析'!$B$7:$B$14</f>
             </numRef>
           </xVal>
           <yVal>
@@ -217,7 +218,7 @@
           </marker>
           <xVal>
             <numRef>
-              <f>'解析'!$A$7:$A$14</f>
+              <f>'解析'!$B$7:$B$14</f>
             </numRef>
           </xVal>
           <yVal>
@@ -227,7 +228,7 @@
           </yVal>
           <smooth val="0"/>
         </ser>
-        <axId val="10"/>
+        <axId val="500"/>
         <axId val="200"/>
       </scatterChart>
       <valAx>
@@ -247,15 +248,18 @@
                   <a:defRPr/>
                 </a:pPr>
                 <a:r>
-                  <a:t>経過時間(s)</a:t>
+                  <a:t>time(ms)</a:t>
                 </a:r>
               </a:p>
             </rich>
           </tx>
+          <overlay val="0"/>
         </title>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
+        <tickLblPos val="low"/>
         <crossAx val="20"/>
+        <crosses val="min"/>
       </valAx>
       <valAx>
         <axId val="20"/>
@@ -279,10 +283,24 @@
               </a:p>
             </rich>
           </tx>
+          <overlay val="0"/>
         </title>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
+        <tickLblPos val="low"/>
         <crossAx val="10"/>
+        <crosses val="min"/>
+      </valAx>
+      <valAx>
+        <axId val="500"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <delete val="1"/>
+        <axPos val="b"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="200"/>
       </valAx>
       <valAx>
         <axId val="200"/>
@@ -305,15 +323,18 @@
               </a:p>
             </rich>
           </tx>
+          <overlay val="0"/>
         </title>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
-        <crossAx val="10"/>
+        <tickLblPos val="high"/>
+        <crossAx val="500"/>
         <crosses val="max"/>
       </valAx>
     </plotArea>
     <legend>
       <legendPos val="b"/>
+      <overlay val="0"/>
     </legend>
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>

--- a/tests/data/expected_log40.xlsx
+++ b/tests/data/expected_log40.xlsx
@@ -24,7 +24,7 @@
     <numFmt numFmtId="165" formatCode="yyyy/mm/dd hh:mm:ss"/>
     <numFmt numFmtId="166" formatCode="yyyy/mm/dd hh:mm:ss.000"/>
   </numFmts>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -32,16 +32,25 @@
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b val="1"/>
+      <sz val="12"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E2EFDA"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="7">
     <border>
       <left/>
       <right/>
@@ -49,13 +58,65 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="00000000"/>
+      </left>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="00000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="00000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00000000"/>
+      </bottom>
+    </border>
+    <border>
+      <right style="thin">
+        <color rgb="00000000"/>
+      </right>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00000000"/>
+      </left>
+      <bottom style="thin">
+        <color rgb="00000000"/>
+      </bottom>
+    </border>
+    <border>
+      <bottom style="thin">
+        <color rgb="00000000"/>
+      </bottom>
+    </border>
+    <border>
+      <right style="thin">
+        <color rgb="00000000"/>
+      </right>
+      <bottom style="thin">
+        <color rgb="00000000"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -655,6 +716,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <tabColor rgb="00A9D08E"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
@@ -697,66 +759,66 @@
     <row r="3"/>
     <row r="4"/>
     <row r="5">
-      <c r="A5" t="inlineStr">
+      <c r="A5" s="2" t="inlineStr">
         <is>
           <t>マイコン内部データ(UART)</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
+      <c r="I5" s="2" t="inlineStr">
         <is>
           <t>測定値</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
+      <c r="A6" s="3" t="inlineStr">
         <is>
           <t>経過時間(s)</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B6" s="3" t="inlineStr">
         <is>
           <t>time(ms)</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="C6" s="3" t="inlineStr">
         <is>
           <t>電圧(mV)</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="D6" s="3" t="inlineStr">
         <is>
           <t>電流(mA)</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="E6" s="3" t="inlineStr">
         <is>
           <t>CAP(mAh)</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="F6" s="3" t="inlineStr">
         <is>
           <t>SOC(％)</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="G6" s="3" t="inlineStr">
         <is>
           <t>温度(℃)</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
+      <c r="I6" s="3" t="inlineStr">
         <is>
           <t>CH1(mV)</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
+      <c r="J6" s="3" t="inlineStr">
         <is>
           <t>CH2(V)</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="n">
+      <c r="A7" s="4" t="n">
         <v>0</v>
       </c>
       <c r="B7" t="n">
@@ -774,18 +836,18 @@
       <c r="F7" t="n">
         <v>17</v>
       </c>
-      <c r="G7" t="n">
+      <c r="G7" s="5" t="n">
         <v>23.8</v>
       </c>
-      <c r="I7" t="n">
+      <c r="I7" s="4" t="n">
         <v>0.28</v>
       </c>
-      <c r="J7" t="n">
+      <c r="J7" s="5" t="n">
         <v>0.0003</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="n">
+      <c r="A8" s="4" t="n">
         <v>1.007</v>
       </c>
       <c r="B8" t="n">
@@ -803,18 +865,18 @@
       <c r="F8" t="n">
         <v>17</v>
       </c>
-      <c r="G8" t="n">
+      <c r="G8" s="5" t="n">
         <v>23.8</v>
       </c>
-      <c r="I8" t="n">
+      <c r="I8" s="4" t="n">
         <v>0.32</v>
       </c>
-      <c r="J8" t="n">
+      <c r="J8" s="5" t="n">
         <v>0.0003</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="n">
+      <c r="A9" s="4" t="n">
         <v>2</v>
       </c>
       <c r="B9" t="n">
@@ -832,18 +894,18 @@
       <c r="F9" t="n">
         <v>17</v>
       </c>
-      <c r="G9" t="n">
+      <c r="G9" s="5" t="n">
         <v>23.8</v>
       </c>
-      <c r="I9" t="n">
+      <c r="I9" s="4" t="n">
         <v>0.34</v>
       </c>
-      <c r="J9" t="n">
+      <c r="J9" s="5" t="n">
         <v>0.0003</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="n">
+      <c r="A10" s="4" t="n">
         <v>3.007</v>
       </c>
       <c r="B10" t="n">
@@ -861,18 +923,18 @@
       <c r="F10" t="n">
         <v>17</v>
       </c>
-      <c r="G10" t="n">
+      <c r="G10" s="5" t="n">
         <v>23.8</v>
       </c>
-      <c r="I10" t="n">
+      <c r="I10" s="4" t="n">
         <v>0.35</v>
       </c>
-      <c r="J10" t="n">
+      <c r="J10" s="5" t="n">
         <v>0.0003</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="n">
+      <c r="A11" s="4" t="n">
         <v>3.999</v>
       </c>
       <c r="B11" t="n">
@@ -890,18 +952,18 @@
       <c r="F11" t="n">
         <v>17</v>
       </c>
-      <c r="G11" t="n">
+      <c r="G11" s="5" t="n">
         <v>23.8</v>
       </c>
-      <c r="I11" t="n">
+      <c r="I11" s="4" t="n">
         <v>0.33</v>
       </c>
-      <c r="J11" t="n">
+      <c r="J11" s="5" t="n">
         <v>0.0003</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="n">
+      <c r="A12" s="4" t="n">
         <v>5.006</v>
       </c>
       <c r="B12" t="n">
@@ -919,18 +981,18 @@
       <c r="F12" t="n">
         <v>17</v>
       </c>
-      <c r="G12" t="n">
+      <c r="G12" s="5" t="n">
         <v>23.8</v>
       </c>
-      <c r="I12" t="n">
+      <c r="I12" s="4" t="n">
         <v>0.31</v>
       </c>
-      <c r="J12" t="n">
+      <c r="J12" s="5" t="n">
         <v>0.0003</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="n">
+      <c r="A13" s="4" t="n">
         <v>5.999</v>
       </c>
       <c r="B13" t="n">
@@ -948,42 +1010,42 @@
       <c r="F13" t="n">
         <v>17</v>
       </c>
-      <c r="G13" t="n">
+      <c r="G13" s="5" t="n">
         <v>23.9</v>
       </c>
-      <c r="I13" t="n">
+      <c r="I13" s="4" t="n">
         <v>0.28</v>
       </c>
-      <c r="J13" t="n">
+      <c r="J13" s="5" t="n">
         <v>0.0003</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="n">
+      <c r="A14" s="6" t="n">
         <v>7.006</v>
       </c>
-      <c r="B14" t="n">
+      <c r="B14" s="7" t="n">
         <v>7000</v>
       </c>
-      <c r="C14" t="n">
+      <c r="C14" s="7" t="n">
         <v>3701</v>
       </c>
-      <c r="D14" t="n">
+      <c r="D14" s="7" t="n">
         <v>-99</v>
       </c>
-      <c r="E14" t="n">
+      <c r="E14" s="7" t="n">
         <v>211</v>
       </c>
-      <c r="F14" t="n">
+      <c r="F14" s="7" t="n">
         <v>17</v>
       </c>
-      <c r="G14" t="n">
+      <c r="G14" s="8" t="n">
         <v>23.8</v>
       </c>
-      <c r="I14" t="n">
+      <c r="I14" s="6" t="n">
         <v>0.21</v>
       </c>
-      <c r="J14" t="n">
+      <c r="J14" s="8" t="n">
         <v>0.0003</v>
       </c>
     </row>
@@ -995,6 +1057,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <tabColor rgb="00F4B084"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
@@ -1066,7 +1129,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="n">
+      <c r="A2" s="9" t="n">
         <v>46289.38187592985</v>
       </c>
       <c r="B2" t="n">
@@ -1098,7 +1161,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="n">
+      <c r="A3" s="9" t="n">
         <v>46289.38188759048</v>
       </c>
       <c r="B3" t="n">
@@ -1130,7 +1193,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="n">
+      <c r="A4" s="9" t="n">
         <v>46289.38189908062</v>
       </c>
       <c r="B4" t="n">
@@ -1162,7 +1225,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="n">
+      <c r="A5" s="9" t="n">
         <v>46289.38191073111</v>
       </c>
       <c r="B5" t="n">
@@ -1194,7 +1257,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="n">
+      <c r="A6" s="9" t="n">
         <v>46289.38192221978</v>
       </c>
       <c r="B6" t="n">
@@ -1226,7 +1289,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="n">
+      <c r="A7" s="9" t="n">
         <v>46289.38193387476</v>
       </c>
       <c r="B7" t="n">
@@ -1258,7 +1321,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="n">
+      <c r="A8" s="9" t="n">
         <v>46289.38194535881</v>
       </c>
       <c r="B8" t="n">
@@ -1290,7 +1353,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="n">
+      <c r="A9" s="9" t="n">
         <v>46289.3819570183</v>
       </c>
       <c r="B9" t="n">

--- a/tests/data/expected_log40.xlsx
+++ b/tests/data/expected_log40.xlsx
@@ -206,7 +206,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>電圧(mV) / 電流(mA)</a:t>
+              <a:t>電圧(mV)  |  電流(mA)</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -225,7 +225,7 @@
           <spPr>
             <a:ln w="19050">
               <a:solidFill>
-                <a:srgbClr val="4472C4"/>
+                <a:srgbClr val="A5A5A5"/>
               </a:solidFill>
               <a:prstDash val="solid"/>
             </a:ln>
@@ -264,7 +264,7 @@
           <spPr>
             <a:ln w="19050">
               <a:solidFill>
-                <a:srgbClr val="ED7D31"/>
+                <a:srgbClr val="FFC000"/>
               </a:solidFill>
               <a:prstDash val="solid"/>
             </a:ln>

--- a/tests/data/expected_log40.xlsx
+++ b/tests/data/expected_log40.xlsx
@@ -50,7 +50,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="7">
+  <borders count="10">
     <border>
       <left/>
       <right/>
@@ -59,9 +59,18 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
+      <left style="medium">
         <color rgb="00000000"/>
       </left>
+      <right style="thin">
+        <color rgb="00000000"/>
+      </right>
+      <top style="medium">
+        <color rgb="00000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00000000"/>
+      </bottom>
     </border>
     <border>
       <left style="thin">
@@ -70,7 +79,7 @@
       <right style="thin">
         <color rgb="00000000"/>
       </right>
-      <top style="thin">
+      <top style="medium">
         <color rgb="00000000"/>
       </top>
       <bottom style="thin">
@@ -78,28 +87,100 @@
       </bottom>
     </border>
     <border>
+      <left style="thin">
+        <color rgb="00000000"/>
+      </left>
+      <right style="medium">
+        <color rgb="00000000"/>
+      </right>
+      <top style="medium">
+        <color rgb="00000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00000000"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="00000000"/>
+      </left>
       <right style="thin">
         <color rgb="00000000"/>
       </right>
+      <top style="thin">
+        <color rgb="00000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00000000"/>
+      </bottom>
     </border>
     <border>
       <left style="thin">
         <color rgb="00000000"/>
       </left>
+      <right style="thin">
+        <color rgb="00000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="00000000"/>
+      </top>
       <bottom style="thin">
         <color rgb="00000000"/>
       </bottom>
     </border>
     <border>
+      <left style="thin">
+        <color rgb="00000000"/>
+      </left>
+      <right style="medium">
+        <color rgb="00000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="00000000"/>
+      </top>
       <bottom style="thin">
         <color rgb="00000000"/>
       </bottom>
     </border>
     <border>
+      <left style="medium">
+        <color rgb="00000000"/>
+      </left>
       <right style="thin">
         <color rgb="00000000"/>
       </right>
-      <bottom style="thin">
+      <top style="thin">
+        <color rgb="00000000"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="00000000"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="00000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="00000000"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="00000000"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00000000"/>
+      </left>
+      <right style="medium">
+        <color rgb="00000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="00000000"/>
+      </top>
+      <bottom style="medium">
         <color rgb="00000000"/>
       </bottom>
     </border>
@@ -107,16 +188,19 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -776,32 +860,32 @@
           <t>経過時間(s)</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B6" s="4" t="inlineStr">
         <is>
           <t>time(ms)</t>
         </is>
       </c>
-      <c r="C6" s="3" t="inlineStr">
+      <c r="C6" s="4" t="inlineStr">
         <is>
           <t>電圧(mV)</t>
         </is>
       </c>
-      <c r="D6" s="3" t="inlineStr">
+      <c r="D6" s="4" t="inlineStr">
         <is>
           <t>電流(mA)</t>
         </is>
       </c>
-      <c r="E6" s="3" t="inlineStr">
+      <c r="E6" s="4" t="inlineStr">
         <is>
           <t>CAP(mAh)</t>
         </is>
       </c>
-      <c r="F6" s="3" t="inlineStr">
+      <c r="F6" s="4" t="inlineStr">
         <is>
           <t>SOC(％)</t>
         </is>
       </c>
-      <c r="G6" s="3" t="inlineStr">
+      <c r="G6" s="5" t="inlineStr">
         <is>
           <t>温度(℃)</t>
         </is>
@@ -811,241 +895,241 @@
           <t>CH1(mV)</t>
         </is>
       </c>
-      <c r="J6" s="3" t="inlineStr">
+      <c r="J6" s="5" t="inlineStr">
         <is>
           <t>CH2(V)</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="4" t="n">
+      <c r="A7" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="B7" t="n">
+      <c r="B7" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="C7" t="n">
+      <c r="C7" s="7" t="n">
         <v>3701</v>
       </c>
-      <c r="D7" t="n">
+      <c r="D7" s="7" t="n">
         <v>-100</v>
       </c>
-      <c r="E7" t="n">
+      <c r="E7" s="7" t="n">
         <v>212</v>
       </c>
-      <c r="F7" t="n">
+      <c r="F7" s="7" t="n">
         <v>17</v>
       </c>
-      <c r="G7" s="5" t="n">
+      <c r="G7" s="8" t="n">
         <v>23.8</v>
       </c>
-      <c r="I7" s="4" t="n">
+      <c r="I7" s="6" t="n">
         <v>0.28</v>
       </c>
-      <c r="J7" s="5" t="n">
+      <c r="J7" s="8" t="n">
         <v>0.0003</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="4" t="n">
+      <c r="A8" s="6" t="n">
         <v>1.007</v>
       </c>
-      <c r="B8" t="n">
+      <c r="B8" s="7" t="n">
         <v>1000</v>
       </c>
-      <c r="C8" t="n">
+      <c r="C8" s="7" t="n">
         <v>3701</v>
       </c>
-      <c r="D8" t="n">
+      <c r="D8" s="7" t="n">
         <v>-100</v>
       </c>
-      <c r="E8" t="n">
+      <c r="E8" s="7" t="n">
         <v>212</v>
       </c>
-      <c r="F8" t="n">
+      <c r="F8" s="7" t="n">
         <v>17</v>
       </c>
-      <c r="G8" s="5" t="n">
+      <c r="G8" s="8" t="n">
         <v>23.8</v>
       </c>
-      <c r="I8" s="4" t="n">
+      <c r="I8" s="6" t="n">
         <v>0.32</v>
       </c>
-      <c r="J8" s="5" t="n">
+      <c r="J8" s="8" t="n">
         <v>0.0003</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="4" t="n">
+      <c r="A9" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="B9" t="n">
+      <c r="B9" s="7" t="n">
         <v>2000</v>
       </c>
-      <c r="C9" t="n">
+      <c r="C9" s="7" t="n">
         <v>3701</v>
       </c>
-      <c r="D9" t="n">
+      <c r="D9" s="7" t="n">
         <v>-100</v>
       </c>
-      <c r="E9" t="n">
+      <c r="E9" s="7" t="n">
         <v>211</v>
       </c>
-      <c r="F9" t="n">
+      <c r="F9" s="7" t="n">
         <v>17</v>
       </c>
-      <c r="G9" s="5" t="n">
+      <c r="G9" s="8" t="n">
         <v>23.8</v>
       </c>
-      <c r="I9" s="4" t="n">
+      <c r="I9" s="6" t="n">
         <v>0.34</v>
       </c>
-      <c r="J9" s="5" t="n">
+      <c r="J9" s="8" t="n">
         <v>0.0003</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="4" t="n">
+      <c r="A10" s="6" t="n">
         <v>3.007</v>
       </c>
-      <c r="B10" t="n">
+      <c r="B10" s="7" t="n">
         <v>3000</v>
       </c>
-      <c r="C10" t="n">
+      <c r="C10" s="7" t="n">
         <v>3701</v>
       </c>
-      <c r="D10" t="n">
+      <c r="D10" s="7" t="n">
         <v>-101</v>
       </c>
-      <c r="E10" t="n">
+      <c r="E10" s="7" t="n">
         <v>211</v>
       </c>
-      <c r="F10" t="n">
+      <c r="F10" s="7" t="n">
         <v>17</v>
       </c>
-      <c r="G10" s="5" t="n">
+      <c r="G10" s="8" t="n">
         <v>23.8</v>
       </c>
-      <c r="I10" s="4" t="n">
+      <c r="I10" s="6" t="n">
         <v>0.35</v>
       </c>
-      <c r="J10" s="5" t="n">
+      <c r="J10" s="8" t="n">
         <v>0.0003</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="4" t="n">
+      <c r="A11" s="6" t="n">
         <v>3.999</v>
       </c>
-      <c r="B11" t="n">
+      <c r="B11" s="7" t="n">
         <v>4000</v>
       </c>
-      <c r="C11" t="n">
+      <c r="C11" s="7" t="n">
         <v>3701</v>
       </c>
-      <c r="D11" t="n">
+      <c r="D11" s="7" t="n">
         <v>-100</v>
       </c>
-      <c r="E11" t="n">
+      <c r="E11" s="7" t="n">
         <v>211</v>
       </c>
-      <c r="F11" t="n">
+      <c r="F11" s="7" t="n">
         <v>17</v>
       </c>
-      <c r="G11" s="5" t="n">
+      <c r="G11" s="8" t="n">
         <v>23.8</v>
       </c>
-      <c r="I11" s="4" t="n">
+      <c r="I11" s="6" t="n">
         <v>0.33</v>
       </c>
-      <c r="J11" s="5" t="n">
+      <c r="J11" s="8" t="n">
         <v>0.0003</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="4" t="n">
+      <c r="A12" s="6" t="n">
         <v>5.006</v>
       </c>
-      <c r="B12" t="n">
+      <c r="B12" s="7" t="n">
         <v>5000</v>
       </c>
-      <c r="C12" t="n">
+      <c r="C12" s="7" t="n">
         <v>3700</v>
       </c>
-      <c r="D12" t="n">
+      <c r="D12" s="7" t="n">
         <v>-100</v>
       </c>
-      <c r="E12" t="n">
+      <c r="E12" s="7" t="n">
         <v>211</v>
       </c>
-      <c r="F12" t="n">
+      <c r="F12" s="7" t="n">
         <v>17</v>
       </c>
-      <c r="G12" s="5" t="n">
+      <c r="G12" s="8" t="n">
         <v>23.8</v>
       </c>
-      <c r="I12" s="4" t="n">
+      <c r="I12" s="6" t="n">
         <v>0.31</v>
       </c>
-      <c r="J12" s="5" t="n">
+      <c r="J12" s="8" t="n">
         <v>0.0003</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="4" t="n">
+      <c r="A13" s="6" t="n">
         <v>5.999</v>
       </c>
-      <c r="B13" t="n">
+      <c r="B13" s="7" t="n">
         <v>6000</v>
       </c>
-      <c r="C13" t="n">
+      <c r="C13" s="7" t="n">
         <v>3701</v>
       </c>
-      <c r="D13" t="n">
+      <c r="D13" s="7" t="n">
         <v>-99</v>
       </c>
-      <c r="E13" t="n">
+      <c r="E13" s="7" t="n">
         <v>211</v>
       </c>
-      <c r="F13" t="n">
+      <c r="F13" s="7" t="n">
         <v>17</v>
       </c>
-      <c r="G13" s="5" t="n">
+      <c r="G13" s="8" t="n">
         <v>23.9</v>
       </c>
-      <c r="I13" s="4" t="n">
+      <c r="I13" s="6" t="n">
         <v>0.28</v>
       </c>
-      <c r="J13" s="5" t="n">
+      <c r="J13" s="8" t="n">
         <v>0.0003</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="6" t="n">
+      <c r="A14" s="9" t="n">
         <v>7.006</v>
       </c>
-      <c r="B14" s="7" t="n">
+      <c r="B14" s="10" t="n">
         <v>7000</v>
       </c>
-      <c r="C14" s="7" t="n">
+      <c r="C14" s="10" t="n">
         <v>3701</v>
       </c>
-      <c r="D14" s="7" t="n">
+      <c r="D14" s="10" t="n">
         <v>-99</v>
       </c>
-      <c r="E14" s="7" t="n">
+      <c r="E14" s="10" t="n">
         <v>211</v>
       </c>
-      <c r="F14" s="7" t="n">
+      <c r="F14" s="10" t="n">
         <v>17</v>
       </c>
-      <c r="G14" s="8" t="n">
+      <c r="G14" s="11" t="n">
         <v>23.8</v>
       </c>
-      <c r="I14" s="6" t="n">
+      <c r="I14" s="9" t="n">
         <v>0.21</v>
       </c>
-      <c r="J14" s="8" t="n">
+      <c r="J14" s="11" t="n">
         <v>0.0003</v>
       </c>
     </row>
@@ -1129,7 +1213,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="9" t="n">
+      <c r="A2" s="12" t="n">
         <v>46289.38187592985</v>
       </c>
       <c r="B2" t="n">
@@ -1161,7 +1245,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="9" t="n">
+      <c r="A3" s="12" t="n">
         <v>46289.38188759048</v>
       </c>
       <c r="B3" t="n">
@@ -1193,7 +1277,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="9" t="n">
+      <c r="A4" s="12" t="n">
         <v>46289.38189908062</v>
       </c>
       <c r="B4" t="n">
@@ -1225,7 +1309,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="9" t="n">
+      <c r="A5" s="12" t="n">
         <v>46289.38191073111</v>
       </c>
       <c r="B5" t="n">
@@ -1257,7 +1341,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="9" t="n">
+      <c r="A6" s="12" t="n">
         <v>46289.38192221978</v>
       </c>
       <c r="B6" t="n">
@@ -1289,7 +1373,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="9" t="n">
+      <c r="A7" s="12" t="n">
         <v>46289.38193387476</v>
       </c>
       <c r="B7" t="n">
@@ -1321,7 +1405,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="9" t="n">
+      <c r="A8" s="12" t="n">
         <v>46289.38194535881</v>
       </c>
       <c r="B8" t="n">
@@ -1353,7 +1437,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="9" t="n">
+      <c r="A9" s="12" t="n">
         <v>46289.3819570183</v>
       </c>
       <c r="B9" t="n">
